--- a/artfynd/A 38648-2025 artfynd.xlsx
+++ b/artfynd/A 38648-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AY73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134704334</v>
+        <v>134745833</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79405</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,37 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Husknoppen, Husknoppen, Dlr</t>
+          <t>Husknoppen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488417</v>
+        <v>488455</v>
       </c>
       <c r="R5" t="n">
-        <v>6825092</v>
+        <v>6825153</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1034,9 +1034,19 @@
           <t>2026-06-27</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1051,22 +1061,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134704740</v>
+        <v>134745840</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79405</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,37 +1084,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Husknoppen, Husknoppen, Dlr</t>
+          <t>Husknoppen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488424</v>
+        <v>488463</v>
       </c>
       <c r="R6" t="n">
-        <v>6825137</v>
+        <v>6825172</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1131,9 +1141,19 @@
           <t>2026-06-27</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1148,22 +1168,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134705015</v>
+        <v>134745841</v>
       </c>
       <c r="B7" t="n">
-        <v>93271</v>
+        <v>79405</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,37 +1191,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Flasktjärnslugnet, Flasktjärnslugnet, Dlr</t>
+          <t>Husknoppen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>488390</v>
+        <v>488444</v>
       </c>
       <c r="R7" t="n">
-        <v>6825227</v>
+        <v>6825175</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1228,9 +1248,19 @@
           <t>2026-06-27</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1245,22 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134705194</v>
+        <v>134745842</v>
       </c>
       <c r="B8" t="n">
-        <v>93271</v>
+        <v>79405</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,46 +1298,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Husknoppen, Husknoppen, Dlr</t>
+          <t>Husknoppen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>488415</v>
+        <v>488442</v>
       </c>
       <c r="R8" t="n">
-        <v>6825229</v>
+        <v>6825160</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1334,9 +1355,19 @@
           <t>2026-06-27</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1351,22 +1382,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134705994</v>
+        <v>134745864</v>
       </c>
       <c r="B9" t="n">
-        <v>91995</v>
+        <v>79405</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1374,37 +1405,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Husknoppen, Husknoppen, Dlr</t>
+          <t>Husknoppen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>488406</v>
+        <v>488408</v>
       </c>
       <c r="R9" t="n">
-        <v>6825266</v>
+        <v>6825323</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1431,9 +1462,19 @@
           <t>2026-06-27</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>20:25</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1448,60 +1489,60 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134704730</v>
+        <v>134745865</v>
       </c>
       <c r="B10" t="n">
-        <v>79373</v>
+        <v>79405</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Flasktjärnslugnet, Flasktjärnslugnet, Dlr</t>
+          <t>Husknoppen, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>488464</v>
+        <v>488401</v>
       </c>
       <c r="R10" t="n">
-        <v>6825135</v>
+        <v>6825322</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1528,9 +1569,19 @@
           <t>2026-06-27</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>20:26</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1545,44 +1596,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134704760</v>
+        <v>134704334</v>
       </c>
       <c r="B11" t="n">
-        <v>79373</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1592,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>488414</v>
+        <v>488417</v>
       </c>
       <c r="R11" t="n">
-        <v>6825152</v>
+        <v>6825092</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1654,32 +1705,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134704880</v>
+        <v>134704740</v>
       </c>
       <c r="B12" t="n">
-        <v>79373</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1689,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488414</v>
+        <v>488424</v>
       </c>
       <c r="R12" t="n">
-        <v>6825171</v>
+        <v>6825137</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1751,32 +1802,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134704881</v>
+        <v>134705015</v>
       </c>
       <c r="B13" t="n">
-        <v>79373</v>
+        <v>93271</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1786,13 +1837,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488464</v>
+        <v>488390</v>
       </c>
       <c r="R13" t="n">
-        <v>6825183</v>
+        <v>6825227</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1848,45 +1899,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134704925</v>
+        <v>134705194</v>
       </c>
       <c r="B14" t="n">
-        <v>79373</v>
+        <v>93271</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Husknoppen, Husknoppen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488424</v>
+        <v>488415</v>
       </c>
       <c r="R14" t="n">
-        <v>6825190</v>
+        <v>6825229</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -1945,48 +2005,57 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134704935</v>
+        <v>134745844</v>
       </c>
       <c r="B15" t="n">
-        <v>79373</v>
+        <v>93271</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Husknoppen, Husknoppen, Dlr</t>
+          <t>Husknoppen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488440</v>
+        <v>488395</v>
       </c>
       <c r="R15" t="n">
-        <v>6825179</v>
+        <v>6825152</v>
       </c>
       <c r="S15" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2013,9 +2082,19 @@
           <t>2026-06-27</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>19:01</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2030,60 +2109,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134704962</v>
+        <v>134705994</v>
       </c>
       <c r="B16" t="n">
-        <v>79373</v>
+        <v>91995</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Flasktjärnslugnet, Flasktjärnslugnet, Dlr</t>
+          <t>Husknoppen, Husknoppen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>488459</v>
+        <v>488406</v>
       </c>
       <c r="R16" t="n">
-        <v>6825230</v>
+        <v>6825266</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2127,19 +2206,19 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134704965</v>
+        <v>134704730</v>
       </c>
       <c r="B17" t="n">
         <v>79373</v>
@@ -2170,17 +2249,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Husknoppen, Husknoppen, Dlr</t>
+          <t>Flasktjärnslugnet, Flasktjärnslugnet, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>488424</v>
+        <v>488464</v>
       </c>
       <c r="R17" t="n">
-        <v>6825162</v>
+        <v>6825135</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2224,19 +2303,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134704975</v>
+        <v>134704760</v>
       </c>
       <c r="B18" t="n">
         <v>79373</v>
@@ -2271,13 +2350,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>488432</v>
+        <v>488414</v>
       </c>
       <c r="R18" t="n">
-        <v>6825158</v>
+        <v>6825152</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2333,7 +2412,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134705037</v>
+        <v>134704880</v>
       </c>
       <c r="B19" t="n">
         <v>79373</v>
@@ -2368,10 +2447,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>488395</v>
+        <v>488414</v>
       </c>
       <c r="R19" t="n">
-        <v>6825194</v>
+        <v>6825171</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2430,7 +2509,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134705093</v>
+        <v>134704881</v>
       </c>
       <c r="B20" t="n">
         <v>79373</v>
@@ -2461,17 +2540,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Husknoppen, Husknoppen, Dlr</t>
+          <t>Flasktjärnslugnet, Flasktjärnslugnet, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>488409</v>
+        <v>488464</v>
       </c>
       <c r="R20" t="n">
-        <v>6825202</v>
+        <v>6825183</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2515,19 +2594,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134705168</v>
+        <v>134704925</v>
       </c>
       <c r="B21" t="n">
         <v>79373</v>
@@ -2562,10 +2641,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>488414</v>
+        <v>488424</v>
       </c>
       <c r="R21" t="n">
-        <v>6825207</v>
+        <v>6825190</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2624,7 +2703,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134705206</v>
+        <v>134704935</v>
       </c>
       <c r="B22" t="n">
         <v>79373</v>
@@ -2655,17 +2734,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Flasktjärnslugnet, Flasktjärnslugnet, Dlr</t>
+          <t>Husknoppen, Husknoppen, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>488332</v>
+        <v>488440</v>
       </c>
       <c r="R22" t="n">
-        <v>6825374</v>
+        <v>6825179</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2709,19 +2788,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134705268</v>
+        <v>134704962</v>
       </c>
       <c r="B23" t="n">
         <v>79373</v>
@@ -2756,10 +2835,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>488267</v>
+        <v>488459</v>
       </c>
       <c r="R23" t="n">
-        <v>6825392</v>
+        <v>6825230</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2818,7 +2897,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134705377</v>
+        <v>134704965</v>
       </c>
       <c r="B24" t="n">
         <v>79373</v>
@@ -2849,17 +2928,17 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Flasktjärnslugnet, Flasktjärnslugnet, Dlr</t>
+          <t>Husknoppen, Husknoppen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>488301</v>
+        <v>488424</v>
       </c>
       <c r="R24" t="n">
-        <v>6825323</v>
+        <v>6825162</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2903,19 +2982,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134705502</v>
+        <v>134704975</v>
       </c>
       <c r="B25" t="n">
         <v>79373</v>
@@ -2950,10 +3029,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>488417</v>
+        <v>488432</v>
       </c>
       <c r="R25" t="n">
-        <v>6825306</v>
+        <v>6825158</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3012,7 +3091,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134706496</v>
+        <v>134705037</v>
       </c>
       <c r="B26" t="n">
         <v>79373</v>
@@ -3043,17 +3122,17 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Flasktjärnslugnet, Flasktjärnslugnet, Dlr</t>
+          <t>Husknoppen, Husknoppen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>488411</v>
+        <v>488395</v>
       </c>
       <c r="R26" t="n">
-        <v>6825306</v>
+        <v>6825194</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3097,19 +3176,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134706558</v>
+        <v>134705093</v>
       </c>
       <c r="B27" t="n">
         <v>79373</v>
@@ -3144,13 +3223,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>488286</v>
+        <v>488409</v>
       </c>
       <c r="R27" t="n">
-        <v>6825379</v>
+        <v>6825202</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3206,32 +3285,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134704527</v>
+        <v>134705168</v>
       </c>
       <c r="B28" t="n">
-        <v>79130</v>
+        <v>79373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3241,13 +3320,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>488417</v>
+        <v>488414</v>
       </c>
       <c r="R28" t="n">
-        <v>6825121</v>
+        <v>6825207</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3303,48 +3382,48 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134705228</v>
+        <v>134705206</v>
       </c>
       <c r="B29" t="n">
-        <v>79130</v>
+        <v>79373</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Husknoppen, Husknoppen, Dlr</t>
+          <t>Flasktjärnslugnet, Flasktjärnslugnet, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>488427</v>
+        <v>488332</v>
       </c>
       <c r="R29" t="n">
-        <v>6825232</v>
+        <v>6825374</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3388,60 +3467,60 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134704390</v>
+        <v>134705268</v>
       </c>
       <c r="B30" t="n">
-        <v>79992</v>
+        <v>79373</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Husknoppen, Husknoppen, Dlr</t>
+          <t>Flasktjärnslugnet, Flasktjärnslugnet, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>488426</v>
+        <v>488267</v>
       </c>
       <c r="R30" t="n">
-        <v>6825098</v>
+        <v>6825392</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3485,60 +3564,60 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134704436</v>
+        <v>134705377</v>
       </c>
       <c r="B31" t="n">
-        <v>79992</v>
+        <v>79373</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Husknoppen, Husknoppen, Dlr</t>
+          <t>Flasktjärnslugnet, Flasktjärnslugnet, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>488418</v>
+        <v>488301</v>
       </c>
       <c r="R31" t="n">
-        <v>6825122</v>
+        <v>6825323</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3582,44 +3661,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134704724</v>
+        <v>134705502</v>
       </c>
       <c r="B32" t="n">
-        <v>79992</v>
+        <v>79373</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3629,13 +3708,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>488424</v>
+        <v>488417</v>
       </c>
       <c r="R32" t="n">
-        <v>6825150</v>
+        <v>6825306</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3691,48 +3770,48 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134706463</v>
+        <v>134706496</v>
       </c>
       <c r="B33" t="n">
-        <v>79992</v>
+        <v>79373</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Husknoppen, Husknoppen, Dlr</t>
+          <t>Flasktjärnslugnet, Flasktjärnslugnet, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>488368</v>
+        <v>488411</v>
       </c>
       <c r="R33" t="n">
-        <v>6825324</v>
+        <v>6825306</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3776,60 +3855,60 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134704649</v>
+        <v>134706558</v>
       </c>
       <c r="B34" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Flasktjärnslugnet, Flasktjärnslugnet, Dlr</t>
+          <t>Husknoppen, Husknoppen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>488445</v>
+        <v>488286</v>
       </c>
       <c r="R34" t="n">
-        <v>6825119</v>
+        <v>6825379</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3859,11 +3938,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-06-27</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på tall.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3878,60 +3952,60 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>lennart karlsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134706271</v>
+        <v>134745835</v>
       </c>
       <c r="B35" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Flasktjärnslugnet, Flasktjärnslugnet, Dlr</t>
+          <t>Husknoppen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>488460</v>
+        <v>488457</v>
       </c>
       <c r="R35" t="n">
-        <v>6825280</v>
+        <v>6825146</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3958,9 +4032,19 @@
           <t>2026-06-27</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>18:44</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3975,60 +4059,60 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134705223</v>
+        <v>134745839</v>
       </c>
       <c r="B36" t="n">
-        <v>79131</v>
+        <v>79373</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Husknoppen, Husknoppen, Dlr</t>
+          <t>Husknoppen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>488427</v>
+        <v>488469</v>
       </c>
       <c r="R36" t="n">
-        <v>6825232</v>
+        <v>6825173</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4055,9 +4139,19 @@
           <t>2026-06-27</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4072,60 +4166,60 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>lennart karlsson</t>
+          <t>Eva Löfqvist</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134706576</v>
+        <v>134745843</v>
       </c>
       <c r="B37" t="n">
-        <v>79131</v>
+        <v>79373</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Husknoppen, Husknoppen, Dlr</t>
+          <t>Husknoppen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>488286</v>
+        <v>488404</v>
       </c>
       <c r="R37" t="n">
-        <v>6825377</v>
+        <v>6825159</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4152,9 +4246,19 @@
           <t>2026-06-27</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4169,15 +4273,3838 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>134745849</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>488368</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6825222</v>
+      </c>
+      <c r="S38" t="n">
+        <v>9</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>134745859</v>
+      </c>
+      <c r="B39" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>488449</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6825238</v>
+      </c>
+      <c r="S39" t="n">
+        <v>9</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>134745860</v>
+      </c>
+      <c r="B40" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>488458</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6825222</v>
+      </c>
+      <c r="S40" t="n">
+        <v>9</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>20:02</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>20:02</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>134745861</v>
+      </c>
+      <c r="B41" t="n">
+        <v>79373</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>488459</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6825267</v>
+      </c>
+      <c r="S41" t="n">
+        <v>8</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>134745850</v>
+      </c>
+      <c r="B42" t="n">
+        <v>78776</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>488380</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6825227</v>
+      </c>
+      <c r="S42" t="n">
+        <v>9</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>19:26</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>19:26</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>134704527</v>
+      </c>
+      <c r="B43" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Husknoppen, Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>488417</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6825121</v>
+      </c>
+      <c r="S43" t="n">
+        <v>20</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
           <t>lennart karlsson</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
+      <c r="AX43" t="inlineStr">
         <is>
           <t>lennart karlsson</t>
         </is>
       </c>
-      <c r="AY37" t="inlineStr"/>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>134705228</v>
+      </c>
+      <c r="B44" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Husknoppen, Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>488427</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6825232</v>
+      </c>
+      <c r="S44" t="n">
+        <v>25</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>134745837</v>
+      </c>
+      <c r="B45" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>488475</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6825166</v>
+      </c>
+      <c r="S45" t="n">
+        <v>12</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>18:49</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>18:49</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>134745852</v>
+      </c>
+      <c r="B46" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>488385</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6825226</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>134745853</v>
+      </c>
+      <c r="B47" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>488377</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6825254</v>
+      </c>
+      <c r="S47" t="n">
+        <v>8</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>134745856</v>
+      </c>
+      <c r="B48" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>488357</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6825265</v>
+      </c>
+      <c r="S48" t="n">
+        <v>5</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>134745857</v>
+      </c>
+      <c r="B49" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>488354</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6825269</v>
+      </c>
+      <c r="S49" t="n">
+        <v>9</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>19:37</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>19:37</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>134704390</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Husknoppen, Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>488426</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6825098</v>
+      </c>
+      <c r="S50" t="n">
+        <v>20</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>134704436</v>
+      </c>
+      <c r="B51" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Husknoppen, Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>488418</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6825122</v>
+      </c>
+      <c r="S51" t="n">
+        <v>20</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>134704724</v>
+      </c>
+      <c r="B52" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Husknoppen, Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>488424</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6825150</v>
+      </c>
+      <c r="S52" t="n">
+        <v>20</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>134706463</v>
+      </c>
+      <c r="B53" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Husknoppen, Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>488368</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6825324</v>
+      </c>
+      <c r="S53" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>134745836</v>
+      </c>
+      <c r="B54" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>488483</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6825155</v>
+      </c>
+      <c r="S54" t="n">
+        <v>8</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>18:48</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>18:48</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>134745838</v>
+      </c>
+      <c r="B55" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>488475</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6825166</v>
+      </c>
+      <c r="S55" t="n">
+        <v>12</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>18:49</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>18:49</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>134745847</v>
+      </c>
+      <c r="B56" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>488379</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6825212</v>
+      </c>
+      <c r="S56" t="n">
+        <v>7</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>134745855</v>
+      </c>
+      <c r="B57" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>488357</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6825265</v>
+      </c>
+      <c r="S57" t="n">
+        <v>5</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>19:35</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>134745867</v>
+      </c>
+      <c r="B58" t="n">
+        <v>79992</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>488290</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6825310</v>
+      </c>
+      <c r="S58" t="n">
+        <v>8</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>134745866</v>
+      </c>
+      <c r="B59" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>488441</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6825319</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>134745863</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>488408</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6825322</v>
+      </c>
+      <c r="S60" t="n">
+        <v>8</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>20:24</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>134745869</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>488270</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6825344</v>
+      </c>
+      <c r="S61" t="n">
+        <v>13</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>20:46</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>20:46</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>134704649</v>
+      </c>
+      <c r="B62" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Flasktjärnslugnet, Flasktjärnslugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>488445</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6825119</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på tall.</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>134706271</v>
+      </c>
+      <c r="B63" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Flasktjärnslugnet, Flasktjärnslugnet, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>488460</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6825280</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Anders Heggestad</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>134745862</v>
+      </c>
+      <c r="B64" t="n">
+        <v>8460</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>488433</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6825312</v>
+      </c>
+      <c r="S64" t="n">
+        <v>5</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>134745830</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>488407</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6825083</v>
+      </c>
+      <c r="S65" t="n">
+        <v>9</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>18:14</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>100 plantor</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>134745868</v>
+      </c>
+      <c r="B66" t="n">
+        <v>99112</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>488249</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6825322</v>
+      </c>
+      <c r="S66" t="n">
+        <v>5</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>20:43</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>134705223</v>
+      </c>
+      <c r="B67" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Husknoppen, Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>488427</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6825232</v>
+      </c>
+      <c r="S67" t="n">
+        <v>25</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>134706576</v>
+      </c>
+      <c r="B68" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Husknoppen, Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>488286</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6825377</v>
+      </c>
+      <c r="S68" t="n">
+        <v>20</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>134745854</v>
+      </c>
+      <c r="B69" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>488373</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6825262</v>
+      </c>
+      <c r="S69" t="n">
+        <v>7</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>19:33</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>134745845</v>
+      </c>
+      <c r="B70" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>488381</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6825132</v>
+      </c>
+      <c r="S70" t="n">
+        <v>7</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>19:03</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>134745846</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>488379</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6825195</v>
+      </c>
+      <c r="S71" t="n">
+        <v>6</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF71" t="inlineStr"/>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>134745848</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>488379</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6825212</v>
+      </c>
+      <c r="S72" t="n">
+        <v>7</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>134745858</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Husknoppen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>488353</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6825250</v>
+      </c>
+      <c r="S73" t="n">
+        <v>12</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Ljusdal</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Los</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-06-27</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38648-2025 artfynd.xlsx
+++ b/artfynd/A 38648-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AZ73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134704630</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134704844</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134705052</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745833</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745840</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745841</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1391,6 +1426,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745842</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1498,6 +1538,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745864</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1605,6 +1650,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745865</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1702,6 +1752,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134704334</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1799,6 +1854,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134704740</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1896,6 +1956,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134705015</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2002,6 +2067,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134705194</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2118,6 +2188,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745844</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2215,6 +2290,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134705994</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2312,6 +2392,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134704730</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2409,6 +2494,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134704760</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2506,6 +2596,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134704880</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2603,6 +2698,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134704881</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2700,6 +2800,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134704925</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2797,6 +2902,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134704935</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2894,6 +3004,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134704962</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2991,6 +3106,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134704965</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3088,6 +3208,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134704975</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3185,6 +3310,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134705037</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3282,6 +3412,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134705093</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3379,6 +3514,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134705168</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3476,6 +3616,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134705206</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3573,6 +3718,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134705268</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3670,6 +3820,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134705377</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3767,6 +3922,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134705502</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3864,6 +4024,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706496</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3961,6 +4126,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706558</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4068,6 +4238,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745835</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4175,6 +4350,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745839</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4282,6 +4462,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745843</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4389,6 +4574,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745849</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4496,6 +4686,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745859</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4603,6 +4798,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745860</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4710,6 +4910,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745861</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4827,6 +5032,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745850</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4924,6 +5134,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134704527</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5021,6 +5236,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134705228</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5128,6 +5348,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745837</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5235,6 +5460,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745852</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5342,6 +5572,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745853</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5449,6 +5684,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745856</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5556,6 +5796,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745857</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5653,6 +5898,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134704390</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5750,6 +6000,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134704436</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5847,6 +6102,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134704724</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5944,6 +6204,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706463</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6051,6 +6316,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745836</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6158,6 +6428,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745838</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6265,6 +6540,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745847</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6372,6 +6652,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745855</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6479,6 +6764,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745867</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6605,6 +6895,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745866</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6717,6 +7012,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745863</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6829,6 +7129,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745869</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6931,6 +7236,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134704649</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7028,6 +7338,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706271</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7140,6 +7455,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745862</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7261,6 +7581,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745830</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7368,6 +7693,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745868</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7465,6 +7795,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134705223</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7562,6 +7897,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134706576</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7669,6 +8009,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745854</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7776,6 +8121,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745845</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7887,6 +8237,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745846</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7998,6 +8353,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745848</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8105,8 +8465,87 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134745858</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>